--- a/absa_data_cleaning/data/interim/watch_t1.1.xlsx
+++ b/absa_data_cleaning/data/interim/watch_t1.1.xlsx
@@ -30634,7 +30634,7 @@
     <row r="791">
       <c r="A791" t="inlineStr">
         <is>
-          <t>Ok giao cũng khá nhanh</t>
+          <t>ẩn danh</t>
         </is>
       </c>
       <c r="B791" t="inlineStr">
@@ -30652,7 +30652,8 @@
       </c>
       <c r="E791" t="inlineStr">
         <is>
-          <t>Đóng gói tạm
+          <t>Ok giao cũng khá nhanh
+Đóng gói tạm
 Có tiếng việt
 Tải app kết nối</t>
         </is>
